--- a/data/Tong_hop_ton_kho.xlsx
+++ b/data/Tong_hop_ton_kho.xlsx
@@ -827,7 +827,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{f0f5726a-71f0-4e34-acfa-f301525c2a0a}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xr:uid="{c8b6d18d-3c61-4f52-9f19-f4c5b110c038}">
   <dimension ref="A1:L38"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
